--- a/data/trans_dic/P25C$smedicoempresa_2023-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P25C$smedicoempresa_2023-Provincia-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo método para dejar de fumar fue, al menos, la ayuda del médico de empresa</t>
+          <t>Población cuyo método para dejar de fumar fue, al menos, la ayuda del médico de empresa (tasa de respuesta: 99,69%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 2,99</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 7,32</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 2,15</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0; 1,81</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0; 2,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,99</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 2,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 2,55</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,16</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,6</t>
+          <t>0,0; 6,9</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0; 1,98</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,09</t>
+          <t>0,0; 3,67</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0; 7,06</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,03</t>
+          <t>0,0; 20,67</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,12</t>
+          <t>0,0; 9,75</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,95</t>
+          <t>0,0; 8,17</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 9,05</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,69</t>
+          <t>0,0; 4,65</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0; 1,33</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0; 1,35</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,67</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0; 1,36</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0; 3,09</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0; 0,95</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,78</t>
+          <t>0,0; 0,86</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,76</t>
+          <t>0,0; 0,57</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,04; 0,66</t>
+          <t>0,06; 0,62</t>
         </is>
       </c>
     </row>
@@ -1029,7 +1029,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo método para dejar de fumar fue, al menos, la ayuda del médico de empresa</t>
+          <t>Población cuyo método para dejar de fumar fue, al menos, la ayuda del médico de empresa (tasa de respuesta: 99,69%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 1422</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 885</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 1284</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 1998</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 1409</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 1740</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 1432</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 1264</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 1366</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 6238</t>
+          <t>0; 6520</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 1150</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 6248</t>
+          <t>0; 5608</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 1045</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 1668</t>
+          <t>0; 1721</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 2341</t>
+          <t>0; 2256</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 3155</t>
+          <t>0; 3709</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 997</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 3208</t>
+          <t>0; 2622</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 1623</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0; 1281</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 1459</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>0; 4710</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>0; 1175</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>0; 3650</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>0; 6642</t>
+          <t>0; 7332</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>0; 2565</t>
+          <t>0; 1917</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>500; 7838</t>
+          <t>701; 7321</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P25C$smedicoempresa_2023-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P25C$smedicoempresa_2023-Provincia-trans_dic.xlsx
@@ -699,7 +699,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -709,7 +709,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>0,96%</t>
         </is>
       </c>
     </row>
@@ -722,7 +722,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,9</t>
+          <t>0,0; 5,17</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,67</t>
+          <t>0,0; 3,76</t>
         </is>
       </c>
     </row>
@@ -754,12 +754,12 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,59%</t>
         </is>
       </c>
     </row>
@@ -777,12 +777,12 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,67</t>
+          <t>0,0; 24,2</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,75</t>
+          <t>0,0; 6,92</t>
         </is>
       </c>
     </row>
@@ -809,7 +809,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,11%</t>
         </is>
       </c>
     </row>
@@ -822,7 +822,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,17</t>
+          <t>0,0; 6,86</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -832,7 +832,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,65</t>
+          <t>0,0; 7,18</t>
         </is>
       </c>
     </row>
@@ -949,7 +949,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -959,7 +959,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,26%</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,86</t>
+          <t>0,09; 1,1</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,57</t>
+          <t>0,0; 0,5</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,62</t>
+          <t>0,06; 0,66</t>
         </is>
       </c>
     </row>
@@ -1330,7 +1330,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>1695</t>
+          <t>1655</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -1340,7 +1340,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1695</t>
+          <t>1655</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 6520</t>
+          <t>0; 5558</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1363,7 +1363,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 5608</t>
+          <t>0; 6481</t>
         </is>
       </c>
     </row>
@@ -1408,12 +1408,12 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>389</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>389</t>
         </is>
       </c>
     </row>
@@ -1431,12 +1431,12 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 1721</t>
+          <t>0; 2137</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 2256</t>
+          <t>0; 1698</t>
         </is>
       </c>
     </row>
@@ -1476,7 +1476,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>636</t>
+          <t>624</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>636</t>
+          <t>624</t>
         </is>
       </c>
     </row>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 3709</t>
+          <t>0; 3056</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 2622</t>
+          <t>0; 4024</t>
         </is>
       </c>
     </row>
@@ -1695,17 +1695,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>2331</t>
+          <t>2279</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>389</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2708</t>
+          <t>2668</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>0; 7332</t>
+          <t>573; 7275</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>0; 1917</t>
+          <t>0; 1844</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>701; 7321</t>
+          <t>627; 6792</t>
         </is>
       </c>
     </row>
